--- a/reports/telegram/aegis_india_2026-09-02.xlsx
+++ b/reports/telegram/aegis_india_2026-09-02.xlsx
@@ -661,10 +661,10 @@
         <v>11475</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11333</v>
+        <v>11310</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-1.24</v>
+        <v>-1.44</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>28</v>
@@ -720,10 +720,10 @@
         <v>391.3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>413.95</v>
+        <v>412.15</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>5.79</v>
+        <v>5.33</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>28</v>
@@ -779,10 +779,10 @@
         <v>5499</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5625.5</v>
+        <v>5800</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.3</v>
+        <v>5.47</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>28</v>
@@ -838,10 +838,10 @@
         <v>2744.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2775.8999</v>
+        <v>2763.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>28</v>
@@ -897,10 +897,10 @@
         <v>709</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>676.2</v>
+        <v>677.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-4.63</v>
+        <v>-4.46</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>29</v>
@@ -956,10 +956,10 @@
         <v>452.35</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>413.55</v>
+        <v>412.3</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-8.58</v>
+        <v>-8.85</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>29</v>
@@ -1015,10 +1015,10 @@
         <v>284.85</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>264.9</v>
+        <v>266.6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-7</v>
+        <v>-6.41</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>29</v>
@@ -1074,10 +1074,10 @@
         <v>113.36</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>113.33</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>-0.03</v>
+        <v>115.22</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.64</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>29</v>
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1205,7 +1205,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=0 · by_state={} · sorted acceptance tier</t>
+          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=3 · by_state={'ACCEPTED': 0, 'WATCH': 2, 'REJECTED': 1, 'NO_EVIDENCE': 0} · sorted acceptance tier</t>
         </is>
       </c>
     </row>
@@ -1267,42 +1267,188 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No R2 decisions/recommendations for 2026-09-02 </t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SUSTAINED_UP</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>verdict=MOMENTUM_WATCH · quality=QUALITY · quality-confirmed momentum · BUT weak</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SUSTAINED_UP</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>verdict=MOMENTUM_WATCH · quality=OK · quality + momentum · BUT overbought · wait</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>QUICK_RISE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>canonical:momentum_ledger</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
+          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Only the active production runner (R2) appears in this workbook.</t>
         </is>
@@ -1314,9 +1460,9 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1328,21 +1474,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1355,7 +1502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 R2 closed positions (last 90d): 37 · latest exit first · realized P&amp;L only</t>
+          <t>📕 Closed positions (last 90d): 38 · latest exit first · realized P&amp;L only · historical accountability incl. retired runners</t>
         </is>
       </c>
     </row>
@@ -1367,55 +1514,60 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Runner</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Exit Date</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Realized P&amp;L %</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
@@ -1424,52 +1576,57 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-ADANIENT-20260902-51452a</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>27</v>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2383.8999</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
-        </is>
+        <v>2863.8999</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>2863.8999</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+57.0pp)</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1478,52 +1635,57 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="4" t="n">
-        <v>398.8</v>
+        <v>27</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>398.8</v>
+        <v>2383.8999</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
-        </is>
+        <v>2160.2</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+13.0pp)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1532,52 +1694,57 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>24</v>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>415.15</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>402.55</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
-        </is>
+        <v>398.8</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+52.9pp)</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1586,52 +1753,57 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>847.5</v>
+        <v>24</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>847.5</v>
+        <v>415.15</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
-        </is>
+        <v>402.55</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-3.04</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+14.3pp)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1640,52 +1812,57 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-MARICO-20260826-1c5a1c</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>1702.7</v>
-      </c>
       <c r="I9" s="4" t="n">
-        <v>1702.7</v>
+        <v>847.5</v>
       </c>
       <c r="J9" s="4" t="n">
+        <v>847.5</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
-        </is>
-      </c>
       <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+56.7pp)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1694,52 +1871,57 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>244.55</v>
-      </c>
       <c r="I10" s="4" t="n">
-        <v>244.55</v>
+        <v>1702.7</v>
       </c>
       <c r="J10" s="4" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
-        </is>
-      </c>
       <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+57.6pp)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1748,52 +1930,57 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-JIOFIN-20260824-89850d</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>402.8</v>
-      </c>
       <c r="I11" s="4" t="n">
-        <v>402.8</v>
+        <v>244.55</v>
       </c>
       <c r="J11" s="4" t="n">
+        <v>244.55</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
-        </is>
-      </c>
       <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+10.1pp)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1802,52 +1989,57 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>1114.2</v>
-      </c>
       <c r="I12" s="4" t="n">
-        <v>1114.2</v>
+        <v>402.8</v>
       </c>
       <c r="J12" s="4" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
-        </is>
-      </c>
       <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+13.3pp)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1856,52 +2048,57 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-MGL-20260821-142d93</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>8693</v>
-      </c>
       <c r="I13" s="4" t="n">
-        <v>8693</v>
+        <v>1114.2</v>
       </c>
       <c r="J13" s="4" t="n">
+        <v>1114.2</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
-        </is>
-      </c>
       <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+14.5pp)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1910,52 +2107,57 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>174.9</v>
-      </c>
       <c r="I14" s="4" t="n">
-        <v>174.9</v>
+        <v>8693</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>8693</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
-        </is>
-      </c>
       <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → GNFC.NS (+61.4pp)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1964,52 +2166,57 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-SAIL-20260820-80f37d</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>14</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>552.4</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
-        </is>
+        <v>174.9</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2018,52 +2225,57 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="H16" s="4" t="n">
-        <v>129.2</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>-3.72</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
-        </is>
+        <v>552.4</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>558</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +14.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2072,52 +2284,57 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="4" t="n">
-        <v>5220</v>
+        <v>13</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5220</v>
+        <v>129.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
-        </is>
+        <v>124.4</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>-3.72</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2126,52 +2343,57 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>12</v>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1327.6</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
-        </is>
+        <v>5220</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>5220</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +60.0pp alpha</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2180,52 +2402,57 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>377</v>
-      </c>
       <c r="I19" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
-        </is>
+        <v>1384</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1327.6</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +56.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2234,52 +2461,57 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>9</v>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11600</v>
+        <v>12</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
-        </is>
+        <v>377</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +9.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2288,52 +2520,57 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" s="4" t="n">
-        <v>3940</v>
+        <v>9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3940</v>
+        <v>11600</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
-        </is>
+        <v>11828</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +6.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2342,52 +2579,57 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>10</v>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2439.3999</v>
+        <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>-3.21</v>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
-        </is>
+        <v>3940</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>3940</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2396,52 +2638,57 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1779.2</v>
+        <v>10</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1779.2</v>
+        <v>2439.3999</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
-        </is>
+        <v>2361</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +6.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2450,52 +2697,57 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
+          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>6</v>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7454.5</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
-        </is>
+        <v>1779.2</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>1779.2</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2504,52 +2756,57 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="4" t="n">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>129</v>
+        <v>7454.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
-        </is>
+        <v>7095</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>-4.82</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +62.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2558,52 +2815,57 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
+          <t>IND-R2-CANBK-20260810-788da8</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>4924</v>
-      </c>
       <c r="I26" s="4" t="n">
-        <v>4924</v>
+        <v>129</v>
       </c>
       <c r="J26" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
-        </is>
-      </c>
       <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +6.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2612,52 +2874,57 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
+          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>181.14</v>
-      </c>
       <c r="I27" s="4" t="n">
-        <v>181.14</v>
+        <v>4924</v>
       </c>
       <c r="J27" s="4" t="n">
+        <v>4924</v>
+      </c>
+      <c r="K27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
-        </is>
-      </c>
       <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +60.1pp alpha</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2666,52 +2933,57 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
+          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6793.5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
-        </is>
+        <v>181.14</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +9.4pp alpha</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2720,52 +2992,57 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H29" s="4" t="n">
-        <v>471.2</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
-        </is>
+        <v>6793.5</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>6774</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2774,52 +3051,57 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H30" s="4" t="n">
-        <v>845</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
-        </is>
+        <v>471.2</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>473.3</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2828,52 +3110,57 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>450</v>
-      </c>
       <c r="I31" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
-        </is>
+        <v>845</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>889.5</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5.27</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2882,52 +3169,57 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>1595</v>
-      </c>
       <c r="I32" s="4" t="n">
-        <v>1584.8</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
-        </is>
+        <v>450</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>-1.6</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2936,52 +3228,57 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>1327.7</v>
-      </c>
       <c r="I33" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
-        </is>
+        <v>1595</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1584.8</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2990,52 +3287,57 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1</v>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2195</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
-        </is>
+        <v>1327.7</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>1285</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>-3.22</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3044,52 +3346,57 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H35" s="4" t="n">
-        <v>1363.6</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
-        </is>
+        <v>2195</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3098,52 +3405,57 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>5470.5</v>
-      </c>
       <c r="I36" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
-        </is>
+        <v>1363.6</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1351.3</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3152,52 +3464,57 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H37" s="4" t="n">
-        <v>1167.5</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
-        </is>
+        <v>5470.5</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>5651.5</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3206,52 +3523,57 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H38" s="4" t="n">
-        <v>268.5</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
-        </is>
+        <v>1167.5</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>1177</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3260,52 +3582,57 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>425.05</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>425.05</v>
+        <v>268.5</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
-        </is>
+        <v>278.8</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3314,52 +3641,57 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+          <t>IND-R2-BIOCON-20260804-954a24</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>939.95</v>
-      </c>
       <c r="I40" s="4" t="n">
-        <v>939.95</v>
+        <v>425.05</v>
       </c>
       <c r="J40" s="4" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+51.8pp)</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -3368,93 +3700,157 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>939.95</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>IND-R2-JSWENERGY-20260804-1210a0</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>JSWENERGY</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>567.3</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>567.3</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>Rotation → LUPIN.NS (+52.0pp)</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Priced: 37 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
+          <t>Priced: 38 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
           <t>This sheet shows the production runner (R2) closed lifecycle only · historical evidence for retired runners lives in canonical audit files only.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:M46"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A47:M47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_india_2026-09-02.xlsx
+++ b/reports/telegram/aegis_india_2026-09-02.xlsx
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.0pp)</t>
+          <t>Rotation swap · +57.0 pp</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.0pp)</t>
+          <t>Rotation swap · +13.0 pp</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+52.9pp)</t>
+          <t>Rotation swap · +52.9 pp</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.3pp)</t>
+          <t>Rotation swap · +14.3 pp</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+56.7pp)</t>
+          <t>Rotation swap · +56.7 pp</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+57.6pp)</t>
+          <t>Rotation swap · +57.6 pp</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+10.1pp)</t>
+          <t>Rotation swap · +10.1 pp</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+13.3pp)</t>
+          <t>Rotation swap · +13.3 pp</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+14.5pp)</t>
+          <t>Rotation swap · +14.5 pp</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GNFC.NS (+61.4pp)</t>
+          <t>Rotation swap · +61.4 pp</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.8pp alpha</t>
+          <t>Outperformance exit · +11.8 pp</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +14.7pp alpha</t>
+          <t>Outperformance exit · +14.7 pp</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +12.2pp alpha</t>
+          <t>Outperformance exit · +12.2 pp</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.0pp alpha</t>
+          <t>Outperformance exit · +60.0 pp</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +56.7pp alpha</t>
+          <t>Outperformance exit · +56.7 pp</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +9.8pp alpha</t>
+          <t>Outperformance exit · +9.8 pp</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.6pp alpha</t>
+          <t>Outperformance exit · +6.6 pp</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.5pp alpha</t>
+          <t>Outperformance exit · +7.5 pp</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +6.7pp alpha</t>
+          <t>Outperformance exit · +6.7 pp</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.1pp alpha</t>
+          <t>Outperformance exit · +8.1 pp</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +62.1pp alpha</t>
+          <t>Outperformance exit · +62.1 pp</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +6.5pp alpha</t>
+          <t>Outperformance exit · +6.5 pp</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +60.1pp alpha</t>
+          <t>Outperformance exit · +60.1 pp</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>→ TCS.NS · +9.4pp alpha</t>
+          <t>Outperformance exit · +9.4 pp</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +8.0pp alpha</t>
+          <t>Outperformance exit · +8.0 pp</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +60.7pp alpha</t>
+          <t>Outperformance exit · +60.7 pp</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.4pp alpha</t>
+          <t>Outperformance exit · +7.4 pp</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.3pp alpha</t>
+          <t>Outperformance exit · +10.3 pp</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +62.5pp alpha</t>
+          <t>Outperformance exit · +62.5 pp</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +64.8pp alpha</t>
+          <t>Outperformance exit · +64.8 pp</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +59.7pp alpha</t>
+          <t>Outperformance exit · +59.7 pp</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +7.8pp alpha</t>
+          <t>Outperformance exit · +7.8 pp</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +10.6pp alpha</t>
+          <t>Outperformance exit · +10.6 pp</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.7pp alpha</t>
+          <t>Outperformance exit · +11.7 pp</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +11.6pp alpha</t>
+          <t>Outperformance exit · +11.6 pp</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>Rotation swap · +51.8 pp</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+51.8pp)</t>
+          <t>Rotation swap · +51.8 pp</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → LUPIN.NS (+52.0pp)</t>
+          <t>Rotation swap · +52.0 pp</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">

--- a/reports/telegram/aegis_india_2026-09-02.xlsx
+++ b/reports/telegram/aegis_india_2026-09-02.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,10 +490,11 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,22 +559,27 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Stop Type</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Engine Verdict</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Would-Have-Exited-On</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>As-Of</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Provenance</t>
         </is>
       </c>
     </row>
@@ -610,29 +616,32 @@
       <c r="H5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I5" s="4" t="n">
+        <v>545.1072</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 4.7% below</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -669,29 +678,32 @@
       <c r="H6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I6" s="4" t="n">
+        <v>10989.5714</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 2.8% below</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -728,29 +740,32 @@
       <c r="H7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I7" s="4" t="n">
+        <v>397.1429</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.6% below</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -787,29 +802,32 @@
       <c r="H8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I8" s="4" t="n">
+        <v>5557.5714</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 4.2% below</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -846,29 +864,32 @@
       <c r="H9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I9" s="4" t="n">
+        <v>2604.7285</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 5.7% below</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -905,29 +926,32 @@
       <c r="H10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I10" s="4" t="n">
+        <v>638.4714</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 5.7% below</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -964,29 +988,32 @@
       <c r="H11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I11" s="4" t="n">
+        <v>399.5571</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.1% below</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1023,29 +1050,32 @@
       <c r="H12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I12" s="4" t="n">
+        <v>258.9929</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 2.9% below</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1082,29 +1112,32 @@
       <c r="H13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I13" s="4" t="n">
+        <v>111.2957</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>HOLD (no trigger)</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>HOLD · stop 3.4% below</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1159,15 +1192,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1179,20 +1212,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1205,264 +1240,239 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📅 Today's R2 decisions/recommendations · ✓ ledger fresh for 2026-09-02 · scanned universe=3 · by_state={'ACCEPTED': 0, 'WATCH': 2, 'REJECTED': 1, 'NO_EVIDENCE': 0} · sorted acceptance tier</t>
+          <t>📅 Today's R2 momentum scan · ✓ ledger fresh for 2026-09-02 · scanned universe=2 · Actions: {'INVEST': 0, 'WATCH': 0, 'AVOID': 2, 'NO EVIDENCE': 0}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Quality Band</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Terminal State</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Entry Zone</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Return 1d %</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Return 5d %</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Return 20d %</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Return 1d %</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Return 5d %</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Return 20d %</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>As-Of</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Attribution</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Provenance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SUSTAINED_UP</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>QUICK_FALL</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>verdict=MOMENTUM_WATCH · quality=QUALITY · quality-confirmed momentum · BUT weak</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2863.8999</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>verdict=AVOID · low quality + falling · structural failure · stay away</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>AVOID</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>JINDALSAW</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
           <t>SUSTAINED_UP</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>verdict=MOMENTUM_WATCH · quality=OK · quality + momentum · BUT overbought · wait</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>QUICK_RISE</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>verdict=PUMP_RISK · big move on low-quality name · pump-and-dump risk · avoid</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:momentum_ledger</t>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Action → INVEST (eligible for new R2 entry today) · WATCH (monitor · do not enter) · AVOID (do not initiate) · NO EVIDENCE (insufficient data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Today + Momentum shows ONLY the current reporting date's R2 decisions/recommendations.</t>
+          <t>Current Price · from canonical parquet close on As-Of · never fabricated.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Terminal states · ACCEPTED · WATCH · REJECTED · NO_EVIDENCE (quality unavailable).</t>
+          <t>Entry Zone / Stop / Confidence · populated when the canonical decision engine provides them · UNAVAILABLE otherwise · zero-fabrication invariant.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday's rows forward.</t>
+          <t>This sheet is REGENERATED from scratch every reporting day · never carries yesterday forward.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>A recommendation does NOT automatically become a Portfolio holding · only canonical lifecycle transitions move a stock into 01_Portfolio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Only the active production runner (R2) appears in this workbook.</t>
+          <t>An INVEST recommendation is a signal · it becomes a Portfolio holding only after canonical lifecycle transition creates a Registry ACTIVE position.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1474,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1488,8 +1498,9 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1502,7 +1513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 Closed positions (last 90d): 38 · latest exit first · realized P&amp;L only · historical accountability incl. retired runners</t>
+          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 administrative/same-day events filtered to canonical audit</t>
         </is>
       </c>
     </row>
@@ -1569,6 +1580,11 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
+          <t>Relative Opportunity pp</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>Provenance</t>
         </is>
       </c>
@@ -1576,17 +1592,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIENT-20260902-51452a</t>
+          <t>IND-R2-LUPIN-20260804-def33a</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1601,32 +1617,35 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2863.8999</v>
+        <v>2383.8999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2863.8999</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>2160.2</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>-9.380000000000001</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +57.0 pp</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1635,17 +1654,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-LUPIN-20260804-def33a</t>
+          <t>IND-R2-COALINDIA-20260804-020cb4</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1665,27 +1684,30 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2383.8999</v>
+        <v>415.15</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2160.2</v>
+        <v>402.55</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-9.380000000000001</v>
+        <v>-3.04</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +13.0 pp</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+          <t>Rotation swap</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1694,17 +1716,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ABCAPITAL-20260831-d36452</t>
+          <t>IND-R2-HINDZINC-20260804-c1073f</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1719,32 +1741,35 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>398.8</v>
+        <v>552.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>398.8</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>558</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +52.9 pp</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1753,17 +1778,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-COALINDIA-20260804-020cb4</t>
+          <t>IND-R2-IEX-20260805-c40707</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1778,32 +1803,35 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>415.15</v>
+        <v>129.2</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>402.55</v>
+        <v>124.4</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-3.04</v>
+        <v>-3.72</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +14.3 pp</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1812,17 +1840,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MARICO-20260826-1c5a1c</t>
+          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1837,32 +1865,35 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>847.5</v>
+        <v>1384</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>847.5</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1327.6</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +56.7 pp</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1871,17 +1902,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TATACOMM-20260825-e3fb82</t>
+          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1896,32 +1927,35 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1702.7</v>
+        <v>377</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1702.7</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>387.55</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +57.6 pp</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1930,17 +1964,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-JIOFIN-20260824-89850d</t>
+          <t>IND-R2-OFSS-20260805-f0f538</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1955,32 +1989,35 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>244.55</v>
+        <v>11600</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>244.55</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>11828</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.97</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +10.1 pp</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -1989,17 +2026,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-KOTAKBANK-20260821-12a4bb</t>
+          <t>IND-R2-TCS-20260804-a45359</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2014,32 +2051,35 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>402.8</v>
+        <v>2439.3999</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>402.8</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>2361</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-3.21</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +13.3 pp</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2048,17 +2088,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-MGL-20260821-142d93</t>
+          <t>IND-R2-AMBER-20260804-0de705</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2073,32 +2113,35 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1114.2</v>
+        <v>7454.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1114.2</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>7095</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-4.82</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +14.5 pp</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2107,17 +2150,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-APOLLOHOSP-20260821-a5649b</t>
+          <t>IND-R2-ATUL-20260805-0e68e6</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2132,32 +2175,35 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8693</v>
+        <v>6793.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8693</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>6774</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Rotation swap · +61.4 pp</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2166,17 +2212,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SAIL-20260820-80f37d</t>
+          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2191,32 +2237,35 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>174.9</v>
+        <v>471.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>473.3</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.45</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +11.8 pp</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2225,17 +2274,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-HINDZINC-20260804-c1073f</t>
+          <t>IND-R2-INDIANB-20260805-70fdf8</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2250,32 +2299,35 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>552.4</v>
+        <v>845</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>558</v>
+        <v>889.5</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.01</v>
+        <v>5.27</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +14.7 pp</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2284,17 +2336,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-IEX-20260805-c40707</t>
+          <t>IND-R2-OIL-20260805-6635e1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2314,27 +2366,30 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>129.2</v>
+        <v>450</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>124.4</v>
+        <v>442.8</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-3.72</v>
+        <v>-1.6</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +12.2 pp</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2343,17 +2398,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-INDIGO-20260818-ebf1a4</t>
+          <t>IND-R2-PRESTIGE-20260805-488bde</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2368,32 +2423,35 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5220</v>
+        <v>1595</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5220</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1584.8</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>-0.64</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +60.0 pp</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2402,17 +2460,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-ADANIGREEN-20260805-4dd183</t>
+          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2432,27 +2490,30 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1384</v>
+        <v>1327.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1327.6</v>
+        <v>1285</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-4.08</v>
+        <v>-3.22</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +56.7 pp</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2461,17 +2522,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-NATIONALUM-20260805-f18c0a</t>
+          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2491,27 +2552,30 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>377</v>
+        <v>2195</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>387.55</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>2.8</v>
+        <v>2182</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-0.59</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +9.8 pp</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2520,12 +2584,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-OFSS-20260805-f0f538</t>
+          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2545,32 +2609,35 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11600</v>
+        <v>1363.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11828</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1.97</v>
+        <v>1351.3</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>-0.9</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +6.6 pp</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2579,17 +2646,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-SIEMENS-20260814-e9c5a1</t>
+          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2604,32 +2671,35 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3940</v>
+        <v>5470.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3940</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>5651.5</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>3.31</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +7.5 pp</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2638,12 +2708,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TCS-20260804-a45359</t>
+          <t>IND-R2-INFY-20260805-ea04e5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2663,32 +2733,35 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2439.3999</v>
+        <v>1167.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2361</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>-3.21</v>
+        <v>1177</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +6.7 pp</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
@@ -2697,12 +2770,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-DEEPAKNTR-20260811-e84d3d</t>
+          <t>IND-R2-VEDL-20260804-563905</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2722,1135 +2795,84 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1779.2</v>
+        <v>268.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1779.2</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>278.8</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Outperformance exit · +8.1 pp</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
+          <t>Outperformance exit</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-AMBER-20260804-0de705</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>7454.5</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>7095</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +62.1 pp</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-CANBK-20260810-788da8</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +6.5 pp</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-TORNTPHARM-20260810-23303f</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>4924</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>4924</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +60.1 pp</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Priced: 20 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-UNIONBANK-20260810-bbc39f</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>181.14</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>181.14</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +9.4 pp</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Realized P&amp;L % · (Exit − Entry) / Entry · own-trade result · positive=green · negative=red.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-ATUL-20260805-0e68e6</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>ATUL</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>6793.5</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +8.0 pp</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Relative Opportunity pp · alpha/rotation benefit vs the closed position (pp = percentage points) · this is NOT the trade's own P&amp;L · shown separately so it cannot be misread.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-DELHIVERY-20260806-840ea5</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>471.2</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +60.7 pp</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>18 same-day / registry-sync administrative events filtered from this operator-facing view · they remain in the canonical Registry JSONL for audit.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-INDIANB-20260805-70fdf8</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>889.5</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +7.4 pp</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-OIL-20260805-6635e1</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>442.8</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +10.3 pp</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-PRESTIGE-20260805-488bde</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1595</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>1584.8</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +62.5 pp</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-VOLTAS-20260805-5c8a00</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>1327.7</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>1285</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +64.8 pp</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-BHARATFORG-20260805-615b4c</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>2195</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +59.7 pp</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-HCLTECH-20260804-5d47d0</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>1363.6</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>1351.3</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +7.8 pp</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-HEROMOTOCO-20260804-4d7633</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>5470.5</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>5651.5</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +10.6 pp</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-INFY-20260805-ea04e5</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>1167.5</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +11.7 pp</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-VEDL-20260804-563905</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>268.5</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>Outperformance exit · +11.6 pp</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-BIOCON-20260804-954a24</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>425.05</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +51.8 pp</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-FORTIS-20260804-6a4e4f</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>939.95</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +51.8 pp</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-JSWENERGY-20260804-1210a0</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>Rotation swap · +52.0 pp</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Priced: 38 · Unpriced (data unavailable): 0 · unpriced rows show — for P&amp;L, never fabricated 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Realized P&amp;L % · (Exit − Entry) / Entry · positive=green · negative=red · zero/N/A=neutral.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>This sheet accumulates closed R2 positions via Registry CLOSED events · latest exit first · 90-day rolling window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>This sheet shows the production runner (R2) closed lifecycle only · historical evidence for retired runners lives in canonical audit files only.</t>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>This sheet contains ONLY realized production exits · 90-day rolling window.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A47:M47"/>
+  <mergeCells count="7">
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_india_2026-09-02.xlsx
+++ b/reports/telegram/aegis_india_2026-09-02.xlsx
@@ -658,15 +658,19 @@
       <c r="I5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>545.1072</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4.68</v>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -686,12 +690,12 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.68% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -748,15 +752,19 @@
       <c r="I6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>10989.5714</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>2.83</v>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -776,12 +784,12 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 2.83% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -838,15 +846,19 @@
       <c r="I7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>397.1429</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>3.64</v>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -866,12 +878,12 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.64% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -928,15 +940,19 @@
       <c r="I8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>5557.5714</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>4.18</v>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -956,12 +972,12 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 4.18% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -1018,15 +1034,19 @@
       <c r="I9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>2604.7285</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>5.74</v>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1046,12 +1066,12 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -1108,15 +1128,19 @@
       <c r="I10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>638.4714</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>5.74</v>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1136,12 +1160,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 5.74% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1198,15 +1222,19 @@
       <c r="I11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>399.5571</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>3.09</v>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1226,12 +1254,12 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.09% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1288,15 +1316,19 @@
       <c r="I12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>258.9929</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>2.85</v>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1316,12 +1348,12 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 2.85% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -1378,15 +1410,19 @@
       <c r="I13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>111.2957</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>3.41</v>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>atr</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1406,12 +1442,12 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>HOLD · stop 3.41% below</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -21281,22 +21317,24 @@
       <c r="I298" s="6" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J298" s="4" t="n">
-        <v>10989.5714</v>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21340,22 +21378,24 @@
       <c r="I299" s="6" t="n">
         <v>-4.46</v>
       </c>
-      <c r="J299" s="4" t="n">
-        <v>638.4714</v>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21399,22 +21439,24 @@
       <c r="I300" s="6" t="n">
         <v>-8.85</v>
       </c>
-      <c r="J300" s="4" t="n">
-        <v>399.5571</v>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21458,22 +21500,24 @@
       <c r="I301" s="5" t="n">
         <v>3.36</v>
       </c>
-      <c r="J301" s="4" t="n">
-        <v>545.1072</v>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21517,22 +21561,24 @@
       <c r="I302" s="6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="J302" s="4" t="n">
-        <v>258.9929</v>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21576,22 +21622,24 @@
       <c r="I303" s="5" t="n">
         <v>5.33</v>
       </c>
-      <c r="J303" s="4" t="n">
-        <v>397.1429</v>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21635,22 +21683,24 @@
       <c r="I304" s="5" t="n">
         <v>5.47</v>
       </c>
-      <c r="J304" s="4" t="n">
-        <v>5557.5714</v>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21694,22 +21744,24 @@
       <c r="I305" s="5" t="n">
         <v>1.64</v>
       </c>
-      <c r="J305" s="4" t="n">
-        <v>111.2957</v>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>
@@ -21753,22 +21805,24 @@
       <c r="I306" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J306" s="4" t="n">
-        <v>2604.7285</v>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>UNAVAILABLE · no canonical stop</t>
         </is>
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices+dynamic_risk_v2</t>
+          <t>canonical:Registry+prices</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_india_2026-09-02.xlsx
+++ b/reports/telegram/aegis_india_2026-09-02.xlsx
@@ -658,19 +658,15 @@
       <c r="I5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J5" s="4" t="n">
+        <v>545.1072</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>4.68</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -690,12 +686,12 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.68% below</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -752,19 +748,15 @@
       <c r="I6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J6" s="4" t="n">
+        <v>10989.5714</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>2.83</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -784,12 +776,12 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 2.83% below</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -846,19 +838,15 @@
       <c r="I7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J7" s="4" t="n">
+        <v>397.1429</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>3.64</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -878,12 +866,12 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.64% below</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -940,19 +928,15 @@
       <c r="I8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J8" s="4" t="n">
+        <v>5557.5714</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>4.18</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -972,12 +956,12 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 4.18% below</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -1034,19 +1018,15 @@
       <c r="I9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J9" s="4" t="n">
+        <v>2604.7285</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>5.74</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1066,12 +1046,12 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.74% below</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -1128,19 +1108,15 @@
       <c r="I10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J10" s="4" t="n">
+        <v>638.4714</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>5.74</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1160,12 +1136,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 5.74% below</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1222,19 +1198,15 @@
       <c r="I11" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J11" s="4" t="n">
+        <v>399.5571</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>3.09</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1254,12 +1226,12 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.09% below</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1316,19 +1288,15 @@
       <c r="I12" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J12" s="4" t="n">
+        <v>258.9929</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>2.85</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1348,12 +1316,12 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 2.85% below</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -1410,19 +1378,15 @@
       <c r="I13" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J13" s="4" t="n">
+        <v>111.2957</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>3.41</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>atr</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1442,12 +1406,12 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD · stop 3.41% below</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -1934,7 +1898,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 administrative/same-day events filtered to canonical audit</t>
+          <t>📕 Realized production exits (last 90d): 20 · latest exit first · realized P&amp;L only · 18 admin (same-day/zero-Δ) + 5 retired-runner events routed to canonical audit sink (orphan_audit_india.jsonl)</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3238,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>18 same-day / registry-sync administrative events filtered from this operator-facing view · they remain in the canonical Registry JSONL for audit.</t>
+          <t>18 same-day / zero-Δ administrative events + 5 retired-runner events filtered from this operator-facing view · they remain in the canonical Registry JSONL and orphan_audit sink for audit.</t>
         </is>
       </c>
     </row>
@@ -21317,24 +21281,22 @@
       <c r="I298" s="6" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J298" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J298" s="4" t="n">
+        <v>10989.5714</v>
       </c>
       <c r="K298" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21378,24 +21340,22 @@
       <c r="I299" s="6" t="n">
         <v>-4.46</v>
       </c>
-      <c r="J299" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J299" s="4" t="n">
+        <v>638.4714</v>
       </c>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21439,24 +21399,22 @@
       <c r="I300" s="6" t="n">
         <v>-8.85</v>
       </c>
-      <c r="J300" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J300" s="4" t="n">
+        <v>399.5571</v>
       </c>
       <c r="K300" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21500,24 +21458,22 @@
       <c r="I301" s="5" t="n">
         <v>3.36</v>
       </c>
-      <c r="J301" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J301" s="4" t="n">
+        <v>545.1072</v>
       </c>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21561,24 +21517,22 @@
       <c r="I302" s="6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="J302" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J302" s="4" t="n">
+        <v>258.9929</v>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21622,24 +21576,22 @@
       <c r="I303" s="5" t="n">
         <v>5.33</v>
       </c>
-      <c r="J303" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J303" s="4" t="n">
+        <v>397.1429</v>
       </c>
       <c r="K303" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21683,24 +21635,22 @@
       <c r="I304" s="5" t="n">
         <v>5.47</v>
       </c>
-      <c r="J304" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J304" s="4" t="n">
+        <v>5557.5714</v>
       </c>
       <c r="K304" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21744,24 +21694,22 @@
       <c r="I305" s="5" t="n">
         <v>1.64</v>
       </c>
-      <c r="J305" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J305" s="4" t="n">
+        <v>111.2957</v>
       </c>
       <c r="K305" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
@@ -21805,24 +21753,22 @@
       <c r="I306" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J306" s="4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+      <c r="J306" s="4" t="n">
+        <v>2604.7285</v>
       </c>
       <c r="K306" s="4" t="inlineStr">
         <is>
-          <t>UNAVAILABLE · no canonical stop</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
         <is>
-          <t>canonical:Registry+prices</t>
+          <t>canonical:Registry+prices+dynamic_risk_v2</t>
         </is>
       </c>
     </row>
